--- a/Pasta_3.xlsx
+++ b/Pasta_3.xlsx
@@ -164,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -176,6 +176,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -533,35 +536,35 @@
       <c r="F2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="5">
         <v>10.36</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="5">
         <v>12.98</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="5">
         <v>16.48</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="5">
         <v>19.21</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="5">
         <v>21.09</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="5">
         <v>14.99</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M2" s="5">
         <v>4.21</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="5">
         <v>0.68</v>
       </c>
-      <c r="O2" s="3">
-        <v>0</v>
-      </c>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
+      <c r="O2" s="5">
+        <v>0</v>
+      </c>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B3" s="3">
@@ -579,37 +582,37 @@
       <c r="F3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="5">
         <v>13.86</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="5">
         <v>15</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="5">
         <v>30.13</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="5">
         <v>18.5</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="5">
         <v>8.77</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="5">
         <v>6.12</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3" s="5">
         <v>3.42</v>
       </c>
-      <c r="N3" s="3">
+      <c r="N3" s="5">
         <v>3.47</v>
       </c>
-      <c r="O3" s="3">
+      <c r="O3" s="5">
         <v>0.74</v>
       </c>
-      <c r="P3" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="3"/>
+      <c r="P3" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="5"/>
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B4" s="3">
@@ -627,35 +630,35 @@
       <c r="F4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="5">
         <v>11.78</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="5">
         <v>12.94</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="5">
         <v>17.93</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="5">
         <v>23.35</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="5">
         <v>23.91</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="5">
         <v>7.59</v>
       </c>
-      <c r="M4" s="3">
+      <c r="M4" s="5">
         <v>2.5</v>
       </c>
-      <c r="N4" s="3">
-        <v>0</v>
-      </c>
-      <c r="O4" s="3">
-        <v>0</v>
-      </c>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
@@ -673,37 +676,37 @@
       <c r="F5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="5">
         <v>12.27</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="5">
         <v>14.17</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="5">
         <v>20.36</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="5">
         <v>32.03</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="5">
         <v>14.17</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="5">
         <v>7</v>
       </c>
-      <c r="M5" s="3">
-        <v>0</v>
-      </c>
-      <c r="N5" s="3">
-        <v>0</v>
-      </c>
-      <c r="O5" s="3">
-        <v>0</v>
-      </c>
-      <c r="P5" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="3"/>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="5"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B6" s="3">
@@ -721,35 +724,35 @@
       <c r="F6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="5">
         <v>22.63</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="5">
         <v>12.4</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="5">
         <v>13.08</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="5">
         <v>17.54</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="5">
         <v>14.91</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="5">
         <v>11.96</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M6" s="5">
         <v>4.1900000000000004</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N6" s="5">
         <v>3.31</v>
       </c>
-      <c r="O6" s="3">
-        <v>0</v>
-      </c>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" s="3">
@@ -767,37 +770,37 @@
       <c r="F7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="5">
         <v>17.399999999999999</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="5">
         <v>14.84</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="5">
         <v>18.43</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="5">
         <v>17.73</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="5">
         <v>16.07</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="5">
         <v>9.5399999999999991</v>
       </c>
-      <c r="M7" s="3">
+      <c r="M7" s="5">
         <v>2.72</v>
       </c>
-      <c r="N7" s="3">
+      <c r="N7" s="5">
         <v>2.74</v>
       </c>
-      <c r="O7" s="3">
+      <c r="O7" s="5">
         <v>0.52</v>
       </c>
-      <c r="P7" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="3"/>
+      <c r="P7" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="5"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" s="3">
@@ -815,35 +818,35 @@
       <c r="F8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="5">
         <v>25.67</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="5">
         <v>13.01</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="5">
         <v>13.12</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="5">
         <v>19.61</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="5">
         <v>9.7899999999999991</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="5">
         <v>11.69</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="5">
         <v>5.77</v>
       </c>
-      <c r="N8" s="3">
+      <c r="N8" s="5">
         <v>1.34</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
+      <c r="O8" s="5">
+        <v>0</v>
+      </c>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B9" s="3">
@@ -861,37 +864,37 @@
       <c r="F9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="5">
         <v>20.97</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="5">
         <v>21.34</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="5">
         <v>21.49</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="5">
         <v>18.059999999999999</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="5">
         <v>9.5399999999999991</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="5">
         <v>2.75</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="5">
         <v>3.09</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="5">
         <v>2.76</v>
       </c>
-      <c r="O9" s="3">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="3">
+      <c r="O9" s="5">
+        <v>0</v>
+      </c>
+      <c r="P9" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="5">
         <v>0</v>
       </c>
     </row>
@@ -911,35 +914,35 @@
       <c r="F10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="5">
         <v>15.74</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="5">
         <v>13.89</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="5">
         <v>20.21</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="5">
         <v>22.35</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="5">
         <v>20.399999999999999</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="5">
         <v>4.58</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="5">
         <v>2.83</v>
       </c>
-      <c r="N10" s="3">
-        <v>0</v>
-      </c>
-      <c r="O10" s="3">
-        <v>0</v>
-      </c>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+      <c r="O10" s="5">
+        <v>0</v>
+      </c>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B11" s="3">
@@ -957,37 +960,37 @@
       <c r="F11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="5">
         <v>12.7</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="5">
         <v>25.86</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="5">
         <v>20.59</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="5">
         <v>17.600000000000001</v>
       </c>
-      <c r="K11" s="3">
+      <c r="K11" s="5">
         <v>13.72</v>
       </c>
-      <c r="L11" s="3">
+      <c r="L11" s="5">
         <v>5.83</v>
       </c>
-      <c r="M11" s="3">
+      <c r="M11" s="5">
         <v>1.75</v>
       </c>
-      <c r="N11" s="3">
+      <c r="N11" s="5">
         <v>1.07</v>
       </c>
-      <c r="O11" s="3">
-        <v>0</v>
-      </c>
-      <c r="P11" s="3">
+      <c r="O11" s="5">
+        <v>0</v>
+      </c>
+      <c r="P11" s="5">
         <v>0.88</v>
       </c>
-      <c r="Q11" s="3"/>
+      <c r="Q11" s="5"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
@@ -1005,35 +1008,35 @@
       <c r="F12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="5">
         <v>20.22</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="5">
         <v>15.32</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="5">
         <v>15.92</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="5">
         <v>15.54</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="5">
         <v>13.77</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="5">
         <v>11.64</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="5">
         <v>6.15</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="5">
         <v>1.43</v>
       </c>
-      <c r="O12" s="3">
-        <v>0</v>
-      </c>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
+      <c r="O12" s="5">
+        <v>0</v>
+      </c>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" s="3">
@@ -1051,37 +1054,37 @@
       <c r="F13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="5">
         <v>22.64</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="5">
         <v>14.47</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="5">
         <v>14.98</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="5">
         <v>20.77</v>
       </c>
-      <c r="K13" s="3">
+      <c r="K13" s="5">
         <v>13.01</v>
       </c>
-      <c r="L13" s="3">
+      <c r="L13" s="5">
         <v>10.64</v>
       </c>
-      <c r="M13" s="3">
+      <c r="M13" s="5">
         <v>3.47</v>
       </c>
-      <c r="N13" s="3">
-        <v>0</v>
-      </c>
-      <c r="O13" s="3">
-        <v>0</v>
-      </c>
-      <c r="P13" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="3">
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+      <c r="O13" s="5">
+        <v>0</v>
+      </c>
+      <c r="P13" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="5">
         <v>0</v>
       </c>
     </row>
@@ -1101,35 +1104,35 @@
       <c r="F14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="5">
         <v>17.48</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="5">
         <v>12.51</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="5">
         <v>19.05</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="5">
         <v>18.84</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="5">
         <v>16.16</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="5">
         <v>10.98</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="5">
         <v>3.68</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="5">
         <v>1.31</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
+      <c r="O14" s="5">
+        <v>0</v>
+      </c>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" s="3">
@@ -1147,37 +1150,37 @@
       <c r="F15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="5">
         <v>26.02</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="5">
         <v>15.31</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="5">
         <v>19.71</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J15" s="5">
         <v>15.93</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="5">
         <v>11.83</v>
       </c>
-      <c r="L15" s="3">
+      <c r="L15" s="5">
         <v>8.83</v>
       </c>
-      <c r="M15" s="3">
+      <c r="M15" s="5">
         <v>1.69</v>
       </c>
-      <c r="N15" s="3">
+      <c r="N15" s="5">
         <v>0.35</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="5">
         <v>0.33</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3">
+      <c r="P15" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="5">
         <v>0</v>
       </c>
     </row>
@@ -1197,35 +1200,35 @@
       <c r="F16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="5">
         <v>22.44</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="5">
         <v>11.14</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I16" s="5">
         <v>15.22</v>
       </c>
-      <c r="J16" s="3">
+      <c r="J16" s="5">
         <v>20.170000000000002</v>
       </c>
-      <c r="K16" s="3">
+      <c r="K16" s="5">
         <v>16.79</v>
       </c>
-      <c r="L16" s="3">
+      <c r="L16" s="5">
         <v>9.02</v>
       </c>
-      <c r="M16" s="3">
+      <c r="M16" s="5">
         <v>3.34</v>
       </c>
-      <c r="N16" s="3">
+      <c r="N16" s="5">
         <v>1.88</v>
       </c>
-      <c r="O16" s="3">
-        <v>0</v>
-      </c>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
+      <c r="O16" s="5">
+        <v>0</v>
+      </c>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" s="3">
@@ -1243,37 +1246,37 @@
       <c r="F17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="5">
         <v>23.86</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="5">
         <v>18.510000000000002</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I17" s="5">
         <v>18.510000000000002</v>
       </c>
-      <c r="J17" s="3">
+      <c r="J17" s="5">
         <v>18.48</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="5">
         <v>10.83</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="5">
         <v>5.73</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="5">
         <v>3.13</v>
       </c>
-      <c r="N17" s="3">
+      <c r="N17" s="5">
         <v>0.95</v>
       </c>
-      <c r="O17" s="3">
-        <v>0</v>
-      </c>
-      <c r="P17" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="3">
+      <c r="O17" s="5">
+        <v>0</v>
+      </c>
+      <c r="P17" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="5">
         <v>0</v>
       </c>
     </row>
@@ -1293,35 +1296,35 @@
       <c r="F18" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="5">
         <v>18.43</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="5">
         <v>13.72</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="5">
         <v>13.1</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J18" s="5">
         <v>18.420000000000002</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="5">
         <v>16.87</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="5">
         <v>11.32</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="5">
         <v>4.88</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N18" s="5">
         <v>3.27</v>
       </c>
-      <c r="O18" s="3">
-        <v>0</v>
-      </c>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
+      <c r="O18" s="5">
+        <v>0</v>
+      </c>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="3">
@@ -1339,37 +1342,37 @@
       <c r="F19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="5">
         <v>23.51</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="5">
         <v>25.08</v>
       </c>
-      <c r="I19" s="3">
+      <c r="I19" s="5">
         <v>19.37</v>
       </c>
-      <c r="J19" s="3">
+      <c r="J19" s="5">
         <v>15.14</v>
       </c>
-      <c r="K19" s="3">
+      <c r="K19" s="5">
         <v>10.29</v>
       </c>
-      <c r="L19" s="3">
+      <c r="L19" s="5">
         <v>1.57</v>
       </c>
-      <c r="M19" s="3">
+      <c r="M19" s="5">
         <v>4.45</v>
       </c>
-      <c r="N19" s="3">
+      <c r="N19" s="5">
         <v>0.59</v>
       </c>
-      <c r="O19" s="3">
-        <v>0</v>
-      </c>
-      <c r="P19" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="3">
+      <c r="O19" s="5">
+        <v>0</v>
+      </c>
+      <c r="P19" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="5">
         <v>0</v>
       </c>
     </row>
@@ -1389,35 +1392,35 @@
       <c r="F20" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="5">
         <v>11.3</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="5">
         <v>12.51</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="5">
         <v>18.649999999999999</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="5">
         <v>18.3</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="5">
         <v>19.559999999999999</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="5">
         <v>10.65</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="5">
         <v>7.98</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20" s="5">
         <v>1.04</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
+      <c r="O20" s="5">
+        <v>0</v>
+      </c>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B21" s="3">
@@ -1435,37 +1438,37 @@
       <c r="F21" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="5">
         <v>7.01</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="5">
         <v>12.11</v>
       </c>
-      <c r="I21" s="3">
+      <c r="I21" s="5">
         <v>15.69</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21" s="5">
         <v>16.57</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="5">
         <v>26.9</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="5">
         <v>16.149999999999999</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="5">
         <v>2.09</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="5">
         <v>1.21</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="5">
         <v>2.2599999999999998</v>
       </c>
-      <c r="P21" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="3"/>
+      <c r="P21" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="5"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B22" s="3">
@@ -1483,35 +1486,35 @@
       <c r="F22" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="5">
         <v>11.63</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22" s="5">
         <v>9.67</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="5">
         <v>18.2</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J22" s="5">
         <v>19.79</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="5">
         <v>21.17</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="5">
         <v>11.27</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="5">
         <v>8.27</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="3"/>
+      <c r="N22" s="5">
+        <v>0</v>
+      </c>
+      <c r="O22" s="5">
+        <v>0</v>
+      </c>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B23" s="3">
@@ -1529,37 +1532,37 @@
       <c r="F23" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G23" s="3">
+      <c r="G23" s="5">
         <v>17.64</v>
       </c>
-      <c r="H23" s="3">
+      <c r="H23" s="5">
         <v>14.01</v>
       </c>
-      <c r="I23" s="3">
+      <c r="I23" s="5">
         <v>18.46</v>
       </c>
-      <c r="J23" s="3">
+      <c r="J23" s="5">
         <v>17.96</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="5">
         <v>18.97</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23" s="5">
         <v>7.97</v>
       </c>
-      <c r="M23" s="3">
+      <c r="M23" s="5">
         <v>3.9</v>
       </c>
-      <c r="N23" s="3">
+      <c r="N23" s="5">
         <v>1.0900000000000001</v>
       </c>
-      <c r="O23" s="3">
-        <v>0</v>
-      </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="3">
+      <c r="O23" s="5">
+        <v>0</v>
+      </c>
+      <c r="P23" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="5">
         <v>0</v>
       </c>
     </row>
@@ -1579,35 +1582,35 @@
       <c r="F24" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="5">
         <v>11.06</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="5">
         <v>10.08</v>
       </c>
-      <c r="I24" s="3">
+      <c r="I24" s="5">
         <v>17.2</v>
       </c>
-      <c r="J24" s="3">
+      <c r="J24" s="5">
         <v>21.53</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="5">
         <v>19.29</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="5">
         <v>16.940000000000001</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="5">
         <v>3.34</v>
       </c>
-      <c r="N24" s="3">
+      <c r="N24" s="5">
         <v>0.56000000000000005</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
+      <c r="O24" s="5">
+        <v>0</v>
+      </c>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B25" s="3">
@@ -1625,37 +1628,37 @@
       <c r="F25" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G25" s="3">
+      <c r="G25" s="5">
         <v>18.21</v>
       </c>
-      <c r="H25" s="3">
+      <c r="H25" s="5">
         <v>12.5</v>
       </c>
-      <c r="I25" s="3">
+      <c r="I25" s="5">
         <v>23.27</v>
       </c>
-      <c r="J25" s="3">
+      <c r="J25" s="5">
         <v>19.190000000000001</v>
       </c>
-      <c r="K25" s="3">
+      <c r="K25" s="5">
         <v>16.34</v>
       </c>
-      <c r="L25" s="3">
+      <c r="L25" s="5">
         <v>6.96</v>
       </c>
-      <c r="M25" s="3">
+      <c r="M25" s="5">
         <v>2.4900000000000002</v>
       </c>
-      <c r="N25" s="3">
+      <c r="N25" s="5">
         <v>0.56000000000000005</v>
       </c>
-      <c r="O25" s="3">
+      <c r="O25" s="5">
         <v>0.48</v>
       </c>
-      <c r="P25" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="3">
+      <c r="P25" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="5">
         <v>0</v>
       </c>
     </row>
@@ -1675,35 +1678,35 @@
       <c r="F26" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G26" s="5">
         <v>16.73</v>
       </c>
-      <c r="H26" s="3">
+      <c r="H26" s="5">
         <v>10.58</v>
       </c>
-      <c r="I26" s="3">
+      <c r="I26" s="5">
         <v>13.96</v>
       </c>
-      <c r="J26" s="3">
+      <c r="J26" s="5">
         <v>22.26</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="5">
         <v>17.760000000000002</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="5">
         <v>12.31</v>
       </c>
-      <c r="M26" s="3">
+      <c r="M26" s="5">
         <v>5.12</v>
       </c>
-      <c r="N26" s="3">
+      <c r="N26" s="5">
         <v>1.27</v>
       </c>
-      <c r="O26" s="3">
-        <v>0</v>
-      </c>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
+      <c r="O26" s="5">
+        <v>0</v>
+      </c>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="5"/>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B27" s="3">
@@ -1721,37 +1724,37 @@
       <c r="F27" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G27" s="3">
+      <c r="G27" s="5">
         <v>19.73</v>
       </c>
-      <c r="H27" s="3">
+      <c r="H27" s="5">
         <v>18.43</v>
       </c>
-      <c r="I27" s="3">
+      <c r="I27" s="5">
         <v>22.94</v>
       </c>
-      <c r="J27" s="3">
+      <c r="J27" s="5">
         <v>17.809999999999999</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="5">
         <v>10.69</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="5">
         <v>7.07</v>
       </c>
-      <c r="M27" s="3">
+      <c r="M27" s="5">
         <v>1.63</v>
       </c>
-      <c r="N27" s="3">
+      <c r="N27" s="5">
         <v>1.28</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="5">
         <v>0.4</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="3">
+      <c r="P27" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="5">
         <v>0</v>
       </c>
     </row>
@@ -1771,35 +1774,35 @@
       <c r="F28" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G28" s="3">
+      <c r="G28" s="5">
         <v>13.91</v>
       </c>
-      <c r="H28" s="3">
+      <c r="H28" s="5">
         <v>6.57</v>
       </c>
-      <c r="I28" s="3">
+      <c r="I28" s="5">
         <v>16.61</v>
       </c>
-      <c r="J28" s="3">
+      <c r="J28" s="5">
         <v>25.77</v>
       </c>
-      <c r="K28" s="3">
+      <c r="K28" s="5">
         <v>19.760000000000002</v>
       </c>
-      <c r="L28" s="3">
+      <c r="L28" s="5">
         <v>12.36</v>
       </c>
-      <c r="M28" s="3">
+      <c r="M28" s="5">
         <v>3.88</v>
       </c>
-      <c r="N28" s="3">
+      <c r="N28" s="5">
         <v>1.1399999999999999</v>
       </c>
-      <c r="O28" s="3">
-        <v>0</v>
-      </c>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
+      <c r="O28" s="5">
+        <v>0</v>
+      </c>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="5"/>
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B29" s="3">
@@ -1817,37 +1820,37 @@
       <c r="F29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G29" s="3">
+      <c r="G29" s="5">
         <v>18.649999999999999</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29" s="5">
         <v>22.36</v>
       </c>
-      <c r="I29" s="3">
+      <c r="I29" s="5">
         <v>27.78</v>
       </c>
-      <c r="J29" s="3">
+      <c r="J29" s="5">
         <v>13.05</v>
       </c>
-      <c r="K29" s="3">
+      <c r="K29" s="5">
         <v>10.47</v>
       </c>
-      <c r="L29" s="3">
+      <c r="L29" s="5">
         <v>3.46</v>
       </c>
-      <c r="M29" s="3">
+      <c r="M29" s="5">
         <v>2.69</v>
       </c>
-      <c r="N29" s="3">
+      <c r="N29" s="5">
         <v>1.1299999999999999</v>
       </c>
-      <c r="O29" s="3">
+      <c r="O29" s="5">
         <v>0.4</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3">
+      <c r="P29" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="5">
         <v>0</v>
       </c>
     </row>
@@ -1867,35 +1870,35 @@
       <c r="F30" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G30" s="3">
+      <c r="G30" s="5">
         <v>16.16</v>
       </c>
-      <c r="H30" s="3">
+      <c r="H30" s="5">
         <v>9.15</v>
       </c>
-      <c r="I30" s="3">
+      <c r="I30" s="5">
         <v>15.94</v>
       </c>
-      <c r="J30" s="3">
+      <c r="J30" s="5">
         <v>22.14</v>
       </c>
-      <c r="K30" s="3">
+      <c r="K30" s="5">
         <v>24.44</v>
       </c>
-      <c r="L30" s="3">
+      <c r="L30" s="5">
         <v>7.74</v>
       </c>
-      <c r="M30" s="3">
+      <c r="M30" s="5">
         <v>1.46</v>
       </c>
-      <c r="N30" s="3">
+      <c r="N30" s="5">
         <v>2.96</v>
       </c>
-      <c r="O30" s="3">
-        <v>0</v>
-      </c>
-      <c r="P30" s="3"/>
-      <c r="Q30" s="3"/>
+      <c r="O30" s="5">
+        <v>0</v>
+      </c>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B31" s="3">
@@ -1913,37 +1916,37 @@
       <c r="F31" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G31" s="3">
+      <c r="G31" s="5">
         <v>13.62</v>
       </c>
-      <c r="H31" s="3">
+      <c r="H31" s="5">
         <v>15.36</v>
       </c>
-      <c r="I31" s="3">
+      <c r="I31" s="5">
         <v>20.55</v>
       </c>
-      <c r="J31" s="3">
+      <c r="J31" s="5">
         <v>21.32</v>
       </c>
-      <c r="K31" s="3">
+      <c r="K31" s="5">
         <v>16.14</v>
       </c>
-      <c r="L31" s="3">
+      <c r="L31" s="5">
         <v>9.98</v>
       </c>
-      <c r="M31" s="3">
+      <c r="M31" s="5">
         <v>2.29</v>
       </c>
-      <c r="N31" s="3">
-        <v>0</v>
-      </c>
-      <c r="O31" s="3">
+      <c r="N31" s="5">
+        <v>0</v>
+      </c>
+      <c r="O31" s="5">
         <v>0.75</v>
       </c>
-      <c r="P31" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="3"/>
+      <c r="P31" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="5"/>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B32" s="3">
@@ -1961,35 +1964,35 @@
       <c r="F32" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="5">
         <v>20.239999999999998</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="5">
         <v>11.96</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="5">
         <v>14.13</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="5">
         <v>17.78</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="5">
         <v>19.61</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="5">
         <v>11.57</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="5">
         <v>3.37</v>
       </c>
-      <c r="N32" s="3">
+      <c r="N32" s="5">
         <v>1.34</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3"/>
-      <c r="Q32" s="3"/>
+      <c r="O32" s="5">
+        <v>0</v>
+      </c>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
     </row>
     <row r="33" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B33" s="3">
@@ -2007,37 +2010,37 @@
       <c r="F33" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G33" s="3">
+      <c r="G33" s="5">
         <v>17.690000000000001</v>
       </c>
-      <c r="H33" s="3">
+      <c r="H33" s="5">
         <v>13.41</v>
       </c>
-      <c r="I33" s="3">
+      <c r="I33" s="5">
         <v>20.72</v>
       </c>
-      <c r="J33" s="3">
+      <c r="J33" s="5">
         <v>23.7</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="5">
         <v>14.81</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L33" s="5">
         <v>5.74</v>
       </c>
-      <c r="M33" s="3">
+      <c r="M33" s="5">
         <v>3.93</v>
       </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
-      <c r="O33" s="3">
-        <v>0</v>
-      </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="3">
+      <c r="N33" s="5">
+        <v>0</v>
+      </c>
+      <c r="O33" s="5">
+        <v>0</v>
+      </c>
+      <c r="P33" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="5">
         <v>0</v>
       </c>
     </row>
@@ -2057,35 +2060,35 @@
       <c r="F34" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G34" s="3">
+      <c r="G34" s="5">
         <v>8.14</v>
       </c>
-      <c r="H34" s="3">
+      <c r="H34" s="5">
         <v>10.55</v>
       </c>
-      <c r="I34" s="3">
+      <c r="I34" s="5">
         <v>15.13</v>
       </c>
-      <c r="J34" s="3">
+      <c r="J34" s="5">
         <v>19.55</v>
       </c>
-      <c r="K34" s="3">
+      <c r="K34" s="5">
         <v>24.43</v>
       </c>
-      <c r="L34" s="3">
+      <c r="L34" s="5">
         <v>10.5</v>
       </c>
-      <c r="M34" s="3">
+      <c r="M34" s="5">
         <v>8.2200000000000006</v>
       </c>
-      <c r="N34" s="3">
+      <c r="N34" s="5">
         <v>3.49</v>
       </c>
-      <c r="O34" s="3">
-        <v>0</v>
-      </c>
-      <c r="P34" s="3"/>
-      <c r="Q34" s="3"/>
+      <c r="O34" s="5">
+        <v>0</v>
+      </c>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="5"/>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B35" s="3">
@@ -2103,37 +2106,37 @@
       <c r="F35" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G35" s="3">
+      <c r="G35" s="5">
         <v>19.93</v>
       </c>
-      <c r="H35" s="3">
+      <c r="H35" s="5">
         <v>5.82</v>
       </c>
-      <c r="I35" s="3">
+      <c r="I35" s="5">
         <v>24.24</v>
       </c>
-      <c r="J35" s="3">
+      <c r="J35" s="5">
         <v>22.06</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="5">
         <v>12.73</v>
       </c>
-      <c r="L35" s="3">
+      <c r="L35" s="5">
         <v>12.93</v>
       </c>
-      <c r="M35" s="3">
+      <c r="M35" s="5">
         <v>2.29</v>
       </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
-      <c r="O35" s="3">
-        <v>0</v>
-      </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="3">
+      <c r="N35" s="5">
+        <v>0</v>
+      </c>
+      <c r="O35" s="5">
+        <v>0</v>
+      </c>
+      <c r="P35" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="5">
         <v>0</v>
       </c>
     </row>
@@ -2153,35 +2156,35 @@
       <c r="F36" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G36" s="3">
+      <c r="G36" s="5">
         <v>16.25</v>
       </c>
-      <c r="H36" s="3">
+      <c r="H36" s="5">
         <v>8.77</v>
       </c>
-      <c r="I36" s="3">
+      <c r="I36" s="5">
         <v>10.01</v>
       </c>
-      <c r="J36" s="3">
+      <c r="J36" s="5">
         <v>20.010000000000002</v>
       </c>
-      <c r="K36" s="3">
+      <c r="K36" s="5">
         <v>22.49</v>
       </c>
-      <c r="L36" s="3">
+      <c r="L36" s="5">
         <v>13.74</v>
       </c>
-      <c r="M36" s="3">
+      <c r="M36" s="5">
         <v>3.75</v>
       </c>
-      <c r="N36" s="3">
+      <c r="N36" s="5">
         <v>4.99</v>
       </c>
-      <c r="O36" s="3">
-        <v>0</v>
-      </c>
-      <c r="P36" s="3"/>
-      <c r="Q36" s="3"/>
+      <c r="O36" s="5">
+        <v>0</v>
+      </c>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="5"/>
     </row>
     <row r="37" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B37" s="3">
@@ -2199,37 +2202,37 @@
       <c r="F37" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G37" s="3">
+      <c r="G37" s="5">
         <v>20.010000000000002</v>
       </c>
-      <c r="H37" s="3">
+      <c r="H37" s="5">
         <v>17.510000000000002</v>
       </c>
-      <c r="I37" s="3">
+      <c r="I37" s="5">
         <v>13.74</v>
       </c>
-      <c r="J37" s="3">
+      <c r="J37" s="5">
         <v>21.25</v>
       </c>
-      <c r="K37" s="3">
+      <c r="K37" s="5">
         <v>16.239999999999998</v>
       </c>
-      <c r="L37" s="3">
+      <c r="L37" s="5">
         <v>7.5</v>
       </c>
-      <c r="M37" s="3">
+      <c r="M37" s="5">
         <v>2.5</v>
       </c>
-      <c r="N37" s="3">
-        <v>0</v>
-      </c>
-      <c r="O37" s="3">
+      <c r="N37" s="5">
+        <v>0</v>
+      </c>
+      <c r="O37" s="5">
         <v>1.25</v>
       </c>
-      <c r="P37" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="3">
+      <c r="P37" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="5">
         <v>0</v>
       </c>
     </row>
@@ -2249,35 +2252,35 @@
       <c r="F38" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G38" s="3">
+      <c r="G38" s="5">
         <v>8.8699999999999992</v>
       </c>
-      <c r="H38" s="3">
+      <c r="H38" s="5">
         <v>9.6</v>
       </c>
-      <c r="I38" s="3">
+      <c r="I38" s="5">
         <v>20.86</v>
       </c>
-      <c r="J38" s="3">
+      <c r="J38" s="5">
         <v>18.559999999999999</v>
       </c>
-      <c r="K38" s="3">
+      <c r="K38" s="5">
         <v>24.01</v>
       </c>
-      <c r="L38" s="3">
+      <c r="L38" s="5">
         <v>11.18</v>
       </c>
-      <c r="M38" s="3">
+      <c r="M38" s="5">
         <v>4</v>
       </c>
-      <c r="N38" s="3">
+      <c r="N38" s="5">
         <v>2.92</v>
       </c>
-      <c r="O38" s="3">
-        <v>0</v>
-      </c>
-      <c r="P38" s="3"/>
-      <c r="Q38" s="3"/>
+      <c r="O38" s="5">
+        <v>0</v>
+      </c>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="5"/>
     </row>
     <row r="39" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B39" s="3">
@@ -2295,37 +2298,37 @@
       <c r="F39" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G39" s="3">
+      <c r="G39" s="5">
         <v>16.63</v>
       </c>
-      <c r="H39" s="3">
+      <c r="H39" s="5">
         <v>18.21</v>
       </c>
-      <c r="I39" s="3">
+      <c r="I39" s="5">
         <v>22.32</v>
       </c>
-      <c r="J39" s="3">
+      <c r="J39" s="5">
         <v>13.6</v>
       </c>
-      <c r="K39" s="3">
+      <c r="K39" s="5">
         <v>12.99</v>
       </c>
-      <c r="L39" s="3">
+      <c r="L39" s="5">
         <v>9.1</v>
       </c>
-      <c r="M39" s="3">
+      <c r="M39" s="5">
         <v>5.57</v>
       </c>
-      <c r="N39" s="3">
+      <c r="N39" s="5">
         <v>0.85</v>
       </c>
-      <c r="O39" s="3">
+      <c r="O39" s="5">
         <v>0.73</v>
       </c>
-      <c r="P39" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="3">
+      <c r="P39" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="5">
         <v>0</v>
       </c>
     </row>
@@ -2345,35 +2348,35 @@
       <c r="F40" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G40" s="3">
+      <c r="G40" s="5">
         <v>7.69</v>
       </c>
-      <c r="H40" s="3">
+      <c r="H40" s="5">
         <v>17.96</v>
       </c>
-      <c r="I40" s="3">
+      <c r="I40" s="5">
         <v>14.9</v>
       </c>
-      <c r="J40" s="3">
+      <c r="J40" s="5">
         <v>23.41</v>
       </c>
-      <c r="K40" s="3">
+      <c r="K40" s="5">
         <v>21.21</v>
       </c>
-      <c r="L40" s="3">
+      <c r="L40" s="5">
         <v>10.6</v>
       </c>
-      <c r="M40" s="3">
+      <c r="M40" s="5">
         <v>3.51</v>
       </c>
-      <c r="N40" s="3">
+      <c r="N40" s="5">
         <v>0.71</v>
       </c>
-      <c r="O40" s="3">
-        <v>0</v>
-      </c>
-      <c r="P40" s="3"/>
-      <c r="Q40" s="3"/>
+      <c r="O40" s="5">
+        <v>0</v>
+      </c>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="5"/>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B41" s="3">
@@ -2391,37 +2394,37 @@
       <c r="F41" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G41" s="3">
+      <c r="G41" s="5">
         <v>18.68</v>
       </c>
-      <c r="H41" s="3">
+      <c r="H41" s="5">
         <v>14.23</v>
       </c>
-      <c r="I41" s="3">
+      <c r="I41" s="5">
         <v>28.15</v>
       </c>
-      <c r="J41" s="3">
+      <c r="J41" s="5">
         <v>14.9</v>
       </c>
-      <c r="K41" s="3">
+      <c r="K41" s="5">
         <v>13.48</v>
       </c>
-      <c r="L41" s="3">
+      <c r="L41" s="5">
         <v>9.19</v>
       </c>
-      <c r="M41" s="3">
+      <c r="M41" s="5">
         <v>1.38</v>
       </c>
-      <c r="N41" s="3">
-        <v>0</v>
-      </c>
-      <c r="O41" s="3">
-        <v>0</v>
-      </c>
-      <c r="P41" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="3"/>
+      <c r="N41" s="5">
+        <v>0</v>
+      </c>
+      <c r="O41" s="5">
+        <v>0</v>
+      </c>
+      <c r="P41" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="5"/>
     </row>
     <row r="42" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B42" s="3">
@@ -2439,35 +2442,35 @@
       <c r="F42" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G42" s="3">
+      <c r="G42" s="5">
         <v>23.79</v>
       </c>
-      <c r="H42" s="3">
+      <c r="H42" s="5">
         <v>15.96</v>
       </c>
-      <c r="I42" s="3">
+      <c r="I42" s="5">
         <v>16.78</v>
       </c>
-      <c r="J42" s="3">
+      <c r="J42" s="5">
         <v>17.95</v>
       </c>
-      <c r="K42" s="3">
+      <c r="K42" s="5">
         <v>12.54</v>
       </c>
-      <c r="L42" s="3">
+      <c r="L42" s="5">
         <v>8.16</v>
       </c>
-      <c r="M42" s="3">
+      <c r="M42" s="5">
         <v>4.04</v>
       </c>
-      <c r="N42" s="3">
+      <c r="N42" s="5">
         <v>0.39</v>
       </c>
-      <c r="O42" s="3">
+      <c r="O42" s="5">
         <v>0.39</v>
       </c>
-      <c r="P42" s="3"/>
-      <c r="Q42" s="3"/>
+      <c r="P42" s="5"/>
+      <c r="Q42" s="5"/>
     </row>
     <row r="43" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B43" s="3">
@@ -2485,37 +2488,37 @@
       <c r="F43" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="5">
         <v>21.53</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="5">
         <v>15.44</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I43" s="5">
         <v>21.2</v>
       </c>
-      <c r="J43" s="3">
+      <c r="J43" s="5">
         <v>17.739999999999998</v>
       </c>
-      <c r="K43" s="3">
+      <c r="K43" s="5">
         <v>12.03</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="5">
         <v>8.94</v>
       </c>
-      <c r="M43" s="3">
+      <c r="M43" s="5">
         <v>1.98</v>
       </c>
-      <c r="N43" s="3">
+      <c r="N43" s="5">
         <v>0.76</v>
       </c>
-      <c r="O43" s="3">
+      <c r="O43" s="5">
         <v>0.38</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="3">
+      <c r="P43" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="5">
         <v>0</v>
       </c>
     </row>
@@ -2535,35 +2538,35 @@
       <c r="F44" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="5">
         <v>17.09</v>
       </c>
-      <c r="H44" s="3">
+      <c r="H44" s="5">
         <v>12.93</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="5">
         <v>19.09</v>
       </c>
-      <c r="J44" s="3">
+      <c r="J44" s="5">
         <v>21.14</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="5">
         <v>17.760000000000002</v>
       </c>
-      <c r="L44" s="3">
+      <c r="L44" s="5">
         <v>9.24</v>
       </c>
-      <c r="M44" s="3">
+      <c r="M44" s="5">
         <v>2.44</v>
       </c>
-      <c r="N44" s="3">
+      <c r="N44" s="5">
         <v>0.3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3"/>
-      <c r="Q44" s="3"/>
+      <c r="O44" s="5">
+        <v>0</v>
+      </c>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="5"/>
     </row>
     <row r="45" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B45" s="3">
@@ -2581,37 +2584,37 @@
       <c r="F45" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="5">
         <v>25.89</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="5">
         <v>17.09</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="5">
         <v>21.13</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="5">
         <v>20.53</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="5">
         <v>12.3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="5">
         <v>2.48</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="5">
         <v>0.56999999999999995</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="N45" s="5">
+        <v>0</v>
+      </c>
+      <c r="O45" s="5">
+        <v>0</v>
+      </c>
+      <c r="P45" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="5">
         <v>0</v>
       </c>
     </row>
@@ -2631,35 +2634,35 @@
       <c r="F46" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G46" s="3">
+      <c r="G46" s="5">
         <v>24.32</v>
       </c>
-      <c r="H46" s="3">
+      <c r="H46" s="5">
         <v>17.89</v>
       </c>
-      <c r="I46" s="3">
+      <c r="I46" s="5">
         <v>19.68</v>
       </c>
-      <c r="J46" s="3">
+      <c r="J46" s="5">
         <v>15.84</v>
       </c>
-      <c r="K46" s="3">
+      <c r="K46" s="5">
         <v>12.31</v>
       </c>
-      <c r="L46" s="3">
+      <c r="L46" s="5">
         <v>7.06</v>
       </c>
-      <c r="M46" s="3">
+      <c r="M46" s="5">
         <v>2.9</v>
       </c>
-      <c r="N46" s="3">
-        <v>0</v>
-      </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
-      <c r="P46" s="3"/>
-      <c r="Q46" s="3"/>
+      <c r="N46" s="5">
+        <v>0</v>
+      </c>
+      <c r="O46" s="5">
+        <v>0</v>
+      </c>
+      <c r="P46" s="5"/>
+      <c r="Q46" s="5"/>
     </row>
     <row r="47" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B47" s="3">
@@ -2677,37 +2680,37 @@
       <c r="F47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="5">
         <v>26.01</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="5">
         <v>25.44</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="5">
         <v>23.06</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="5">
         <v>13.34</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="5">
         <v>8.8699999999999992</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="5">
         <v>1.61</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="5">
         <v>1.22</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47" s="5">
         <v>0.44</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3">
+      <c r="O47" s="5">
+        <v>0</v>
+      </c>
+      <c r="P47" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="5">
         <v>0</v>
       </c>
     </row>
@@ -2727,35 +2730,35 @@
       <c r="F48" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G48" s="3">
+      <c r="G48" s="5">
         <v>43.16</v>
       </c>
-      <c r="H48" s="3">
+      <c r="H48" s="5">
         <v>17.07</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="5">
         <v>10.050000000000001</v>
       </c>
-      <c r="J48" s="3">
+      <c r="J48" s="5">
         <v>12.86</v>
       </c>
-      <c r="K48" s="3">
+      <c r="K48" s="5">
         <v>10.48</v>
       </c>
-      <c r="L48" s="3">
+      <c r="L48" s="5">
         <v>5.55</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="5">
         <v>0.83</v>
       </c>
-      <c r="N48" s="3">
-        <v>0</v>
-      </c>
-      <c r="O48" s="3">
-        <v>0</v>
-      </c>
-      <c r="P48" s="3"/>
-      <c r="Q48" s="3"/>
+      <c r="N48" s="5">
+        <v>0</v>
+      </c>
+      <c r="O48" s="5">
+        <v>0</v>
+      </c>
+      <c r="P48" s="5"/>
+      <c r="Q48" s="5"/>
     </row>
     <row r="49" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B49" s="3">
@@ -2773,37 +2776,37 @@
       <c r="F49" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G49" s="3">
+      <c r="G49" s="5">
         <v>27.01</v>
       </c>
-      <c r="H49" s="3">
+      <c r="H49" s="5">
         <v>24.11</v>
       </c>
-      <c r="I49" s="3">
+      <c r="I49" s="5">
         <v>23.55</v>
       </c>
-      <c r="J49" s="3">
+      <c r="J49" s="5">
         <v>17.25</v>
       </c>
-      <c r="K49" s="3">
+      <c r="K49" s="5">
         <v>4.1100000000000003</v>
       </c>
-      <c r="L49" s="3">
+      <c r="L49" s="5">
         <v>1.59</v>
       </c>
-      <c r="M49" s="3">
+      <c r="M49" s="5">
         <v>2.38</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
-      <c r="P49" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="3">
+      <c r="N49" s="5">
+        <v>0</v>
+      </c>
+      <c r="O49" s="5">
+        <v>0</v>
+      </c>
+      <c r="P49" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="5">
         <v>0</v>
       </c>
     </row>
@@ -2823,35 +2826,35 @@
       <c r="F50" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G50" s="3">
+      <c r="G50" s="5">
         <v>12.35</v>
       </c>
-      <c r="H50" s="3">
+      <c r="H50" s="5">
         <v>8.5399999999999991</v>
       </c>
-      <c r="I50" s="3">
+      <c r="I50" s="5">
         <v>16.48</v>
       </c>
-      <c r="J50" s="3">
+      <c r="J50" s="5">
         <v>20.59</v>
       </c>
-      <c r="K50" s="3">
+      <c r="K50" s="5">
         <v>29.97</v>
       </c>
-      <c r="L50" s="3">
+      <c r="L50" s="5">
         <v>7.51</v>
       </c>
-      <c r="M50" s="3">
+      <c r="M50" s="5">
         <v>3.97</v>
       </c>
-      <c r="N50" s="3">
+      <c r="N50" s="5">
         <v>0.6</v>
       </c>
-      <c r="O50" s="3">
-        <v>0</v>
-      </c>
-      <c r="P50" s="3"/>
-      <c r="Q50" s="3"/>
+      <c r="O50" s="5">
+        <v>0</v>
+      </c>
+      <c r="P50" s="5"/>
+      <c r="Q50" s="5"/>
     </row>
     <row r="51" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B51" s="3">
@@ -2869,37 +2872,37 @@
       <c r="F51" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G51" s="3">
+      <c r="G51" s="5">
         <v>13.54</v>
       </c>
-      <c r="H51" s="3">
+      <c r="H51" s="5">
         <v>15.96</v>
       </c>
-      <c r="I51" s="3">
+      <c r="I51" s="5">
         <v>24.76</v>
       </c>
-      <c r="J51" s="3">
+      <c r="J51" s="5">
         <v>24.6</v>
       </c>
-      <c r="K51" s="3">
+      <c r="K51" s="5">
         <v>11.6</v>
       </c>
-      <c r="L51" s="3">
+      <c r="L51" s="5">
         <v>6.73</v>
       </c>
-      <c r="M51" s="3">
+      <c r="M51" s="5">
         <v>2.2200000000000002</v>
       </c>
-      <c r="N51" s="3">
+      <c r="N51" s="5">
         <v>0.6</v>
       </c>
-      <c r="O51" s="3">
-        <v>0</v>
-      </c>
-      <c r="P51" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="3"/>
+      <c r="O51" s="5">
+        <v>0</v>
+      </c>
+      <c r="P51" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="5"/>
     </row>
     <row r="52" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B52" s="3">
@@ -2917,35 +2920,35 @@
       <c r="F52" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G52" s="3">
+      <c r="G52" s="5">
         <v>19.3</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="5">
         <v>10.81</v>
       </c>
-      <c r="I52" s="3">
+      <c r="I52" s="5">
         <v>12.9</v>
       </c>
-      <c r="J52" s="3">
+      <c r="J52" s="5">
         <v>16</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="5">
         <v>21.92</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="5">
         <v>12.95</v>
       </c>
-      <c r="M52" s="3">
+      <c r="M52" s="5">
         <v>5.52</v>
       </c>
-      <c r="N52" s="3">
+      <c r="N52" s="5">
         <v>0.61</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3"/>
-      <c r="Q52" s="3"/>
+      <c r="O52" s="5">
+        <v>0</v>
+      </c>
+      <c r="P52" s="5"/>
+      <c r="Q52" s="5"/>
     </row>
     <row r="53" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B53" s="3">
@@ -2963,37 +2966,37 @@
       <c r="F53" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G53" s="3">
+      <c r="G53" s="5">
         <v>14.97</v>
       </c>
-      <c r="H53" s="3">
+      <c r="H53" s="5">
         <v>17.440000000000001</v>
       </c>
-      <c r="I53" s="3">
+      <c r="I53" s="5">
         <v>19.329999999999998</v>
       </c>
-      <c r="J53" s="3">
+      <c r="J53" s="5">
         <v>22.24</v>
       </c>
-      <c r="K53" s="3">
+      <c r="K53" s="5">
         <v>14.15</v>
       </c>
-      <c r="L53" s="3">
+      <c r="L53" s="5">
         <v>10.01</v>
       </c>
-      <c r="M53" s="3">
+      <c r="M53" s="5">
         <v>1.19</v>
       </c>
-      <c r="N53" s="3">
-        <v>0</v>
-      </c>
-      <c r="O53" s="3">
+      <c r="N53" s="5">
+        <v>0</v>
+      </c>
+      <c r="O53" s="5">
         <v>0.67</v>
       </c>
-      <c r="P53" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="3"/>
+      <c r="P53" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="5"/>
     </row>
     <row r="54" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B54" s="3">
@@ -3011,35 +3014,35 @@
       <c r="F54" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G54" s="3">
+      <c r="G54" s="5">
         <v>7.44</v>
       </c>
-      <c r="H54" s="3">
+      <c r="H54" s="5">
         <v>8.9499999999999993</v>
       </c>
-      <c r="I54" s="3">
+      <c r="I54" s="5">
         <v>14.92</v>
       </c>
-      <c r="J54" s="3">
+      <c r="J54" s="5">
         <v>17.86</v>
       </c>
-      <c r="K54" s="3">
+      <c r="K54" s="5">
         <v>29.8</v>
       </c>
-      <c r="L54" s="3">
+      <c r="L54" s="5">
         <v>16.52</v>
       </c>
-      <c r="M54" s="3">
+      <c r="M54" s="5">
         <v>2.98</v>
       </c>
-      <c r="N54" s="3">
+      <c r="N54" s="5">
         <v>1.51</v>
       </c>
-      <c r="O54" s="3">
-        <v>0</v>
-      </c>
-      <c r="P54" s="3"/>
-      <c r="Q54" s="3"/>
+      <c r="O54" s="5">
+        <v>0</v>
+      </c>
+      <c r="P54" s="5"/>
+      <c r="Q54" s="5"/>
     </row>
     <row r="55" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B55" s="3">
@@ -3057,37 +3060,37 @@
       <c r="F55" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G55" s="3">
+      <c r="G55" s="5">
         <v>13.45</v>
       </c>
-      <c r="H55" s="3">
+      <c r="H55" s="5">
         <v>16.309999999999999</v>
       </c>
-      <c r="I55" s="3">
+      <c r="I55" s="5">
         <v>17.91</v>
       </c>
-      <c r="J55" s="3">
+      <c r="J55" s="5">
         <v>23.79</v>
       </c>
-      <c r="K55" s="3">
+      <c r="K55" s="5">
         <v>15.05</v>
       </c>
-      <c r="L55" s="3">
+      <c r="L55" s="5">
         <v>9</v>
       </c>
-      <c r="M55" s="3">
+      <c r="M55" s="5">
         <v>1.47</v>
       </c>
-      <c r="N55" s="3">
+      <c r="N55" s="5">
         <v>1.51</v>
       </c>
-      <c r="O55" s="3">
-        <v>0</v>
-      </c>
-      <c r="P55" s="3">
+      <c r="O55" s="5">
+        <v>0</v>
+      </c>
+      <c r="P55" s="5">
         <v>1.51</v>
       </c>
-      <c r="Q55" s="3">
+      <c r="Q55" s="5">
         <v>0</v>
       </c>
     </row>
@@ -3107,35 +3110,35 @@
       <c r="F56" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G56" s="3">
+      <c r="G56" s="5">
         <v>15.38</v>
       </c>
-      <c r="H56" s="3">
+      <c r="H56" s="5">
         <v>15.38</v>
       </c>
-      <c r="I56" s="3">
+      <c r="I56" s="5">
         <v>19.23</v>
       </c>
-      <c r="J56" s="3">
+      <c r="J56" s="5">
         <v>7.69</v>
       </c>
-      <c r="K56" s="3">
+      <c r="K56" s="5">
         <v>11.54</v>
       </c>
-      <c r="L56" s="3">
+      <c r="L56" s="5">
         <v>23.08</v>
       </c>
-      <c r="M56" s="3">
-        <v>0</v>
-      </c>
-      <c r="N56" s="3">
+      <c r="M56" s="5">
+        <v>0</v>
+      </c>
+      <c r="N56" s="5">
         <v>7.69</v>
       </c>
-      <c r="O56" s="3">
-        <v>0</v>
-      </c>
-      <c r="P56" s="3"/>
-      <c r="Q56" s="3"/>
+      <c r="O56" s="5">
+        <v>0</v>
+      </c>
+      <c r="P56" s="5"/>
+      <c r="Q56" s="5"/>
     </row>
     <row r="57" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B57" s="3">
@@ -3153,37 +3156,37 @@
       <c r="F57" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G57" s="3">
+      <c r="G57" s="5">
         <v>15.38</v>
       </c>
-      <c r="H57" s="3">
+      <c r="H57" s="5">
         <v>26.92</v>
       </c>
-      <c r="I57" s="3">
+      <c r="I57" s="5">
         <v>19.23</v>
       </c>
-      <c r="J57" s="3">
+      <c r="J57" s="5">
         <v>7.69</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="5">
         <v>19.23</v>
       </c>
-      <c r="L57" s="3">
+      <c r="L57" s="5">
         <v>3.85</v>
       </c>
-      <c r="M57" s="3">
+      <c r="M57" s="5">
         <v>7.69</v>
       </c>
-      <c r="N57" s="3">
-        <v>0</v>
-      </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="3">
+      <c r="N57" s="5">
+        <v>0</v>
+      </c>
+      <c r="O57" s="5">
+        <v>0</v>
+      </c>
+      <c r="P57" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="5">
         <v>0</v>
       </c>
     </row>
@@ -3203,35 +3206,35 @@
       <c r="F58" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G58" s="3">
+      <c r="G58" s="5">
         <v>18.600000000000001</v>
       </c>
-      <c r="H58" s="3">
+      <c r="H58" s="5">
         <v>18.21</v>
       </c>
-      <c r="I58" s="3">
+      <c r="I58" s="5">
         <v>18.260000000000002</v>
       </c>
-      <c r="J58" s="3">
+      <c r="J58" s="5">
         <v>22.45</v>
       </c>
-      <c r="K58" s="3">
+      <c r="K58" s="5">
         <v>12.84</v>
       </c>
-      <c r="L58" s="3">
+      <c r="L58" s="5">
         <v>4.87</v>
       </c>
-      <c r="M58" s="3">
+      <c r="M58" s="5">
         <v>3.17</v>
       </c>
-      <c r="N58" s="3">
+      <c r="N58" s="5">
         <v>0.79</v>
       </c>
-      <c r="O58" s="3">
+      <c r="O58" s="5">
         <v>0.79</v>
       </c>
-      <c r="P58" s="3"/>
-      <c r="Q58" s="3"/>
+      <c r="P58" s="5"/>
+      <c r="Q58" s="5"/>
     </row>
     <row r="59" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B59" s="3">
@@ -3249,37 +3252,37 @@
       <c r="F59" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59" s="5">
         <v>22.9</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="5">
         <v>22.71</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="5">
         <v>22.41</v>
       </c>
-      <c r="J59" s="3">
+      <c r="J59" s="5">
         <v>14.46</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="5">
         <v>9.36</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="5">
         <v>4.08</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="5">
         <v>4.08</v>
       </c>
-      <c r="N59" s="3">
-        <v>0</v>
-      </c>
-      <c r="O59" s="3">
-        <v>0</v>
-      </c>
-      <c r="P59" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="3">
+      <c r="N59" s="5">
+        <v>0</v>
+      </c>
+      <c r="O59" s="5">
+        <v>0</v>
+      </c>
+      <c r="P59" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="5">
         <v>0</v>
       </c>
     </row>
@@ -3299,37 +3302,37 @@
       <c r="F60" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G60" s="3">
+      <c r="G60" s="5">
         <v>17.75</v>
       </c>
-      <c r="H60" s="3">
+      <c r="H60" s="5">
         <v>12.83</v>
       </c>
-      <c r="I60" s="3">
+      <c r="I60" s="5">
         <v>16.13</v>
       </c>
-      <c r="J60" s="3">
+      <c r="J60" s="5">
         <v>17.75</v>
       </c>
-      <c r="K60" s="3">
+      <c r="K60" s="5">
         <v>14.03</v>
       </c>
-      <c r="L60" s="3">
+      <c r="L60" s="5">
         <v>10.55</v>
       </c>
-      <c r="M60" s="3">
+      <c r="M60" s="5">
         <v>6</v>
       </c>
-      <c r="N60" s="3">
+      <c r="N60" s="5">
         <v>2.97</v>
       </c>
-      <c r="O60" s="3">
+      <c r="O60" s="5">
         <v>1.49</v>
       </c>
-      <c r="P60" s="3">
+      <c r="P60" s="5">
         <v>0.51</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="Q60" s="5">
         <v>0</v>
       </c>
     </row>
@@ -3349,37 +3352,37 @@
       <c r="F61" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G61" s="3">
+      <c r="G61" s="5">
         <v>18.2</v>
       </c>
-      <c r="H61" s="3">
+      <c r="H61" s="5">
         <v>12.61</v>
       </c>
-      <c r="I61" s="3">
+      <c r="I61" s="5">
         <v>15.82</v>
       </c>
-      <c r="J61" s="3">
+      <c r="J61" s="5">
         <v>17.27</v>
       </c>
-      <c r="K61" s="3">
+      <c r="K61" s="5">
         <v>14.37</v>
       </c>
-      <c r="L61" s="3">
+      <c r="L61" s="5">
         <v>10.4</v>
       </c>
-      <c r="M61" s="3">
+      <c r="M61" s="5">
         <v>6.16</v>
       </c>
-      <c r="N61" s="3">
+      <c r="N61" s="5">
         <v>3.13</v>
       </c>
-      <c r="O61" s="3">
+      <c r="O61" s="5">
         <v>1.48</v>
       </c>
-      <c r="P61" s="3">
+      <c r="P61" s="5">
         <v>0.56000000000000005</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="Q61" s="5">
         <v>0</v>
       </c>
     </row>
@@ -3399,35 +3402,35 @@
       <c r="F62" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62" s="5">
         <v>16.52</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="5">
         <v>11.4</v>
       </c>
-      <c r="I62" s="3">
+      <c r="I62" s="5">
         <v>14.96</v>
       </c>
-      <c r="J62" s="3">
+      <c r="J62" s="5">
         <v>17.29</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="5">
         <v>17.21</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="5">
         <v>13.56</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="5">
         <v>7.11</v>
       </c>
-      <c r="N62" s="3">
+      <c r="N62" s="5">
         <v>1.9</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="5">
         <v>0.06</v>
       </c>
-      <c r="P62" s="3"/>
-      <c r="Q62" s="3"/>
+      <c r="P62" s="5"/>
+      <c r="Q62" s="5"/>
     </row>
     <row r="63" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B63" s="3">
@@ -3445,35 +3448,35 @@
       <c r="F63" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G63" s="3">
+      <c r="G63" s="5">
         <v>17.14</v>
       </c>
-      <c r="H63" s="3">
+      <c r="H63" s="5">
         <v>11.83</v>
       </c>
-      <c r="I63" s="3">
+      <c r="I63" s="5">
         <v>15.19</v>
       </c>
-      <c r="J63" s="3">
+      <c r="J63" s="5">
         <v>17</v>
       </c>
-      <c r="K63" s="3">
+      <c r="K63" s="5">
         <v>16.54</v>
       </c>
-      <c r="L63" s="3">
+      <c r="L63" s="5">
         <v>13.26</v>
       </c>
-      <c r="M63" s="3">
+      <c r="M63" s="5">
         <v>7.11</v>
       </c>
-      <c r="N63" s="3">
+      <c r="N63" s="5">
         <v>1.85</v>
       </c>
-      <c r="O63" s="3">
+      <c r="O63" s="5">
         <v>0.08</v>
       </c>
-      <c r="P63" s="3"/>
-      <c r="Q63" s="3"/>
+      <c r="P63" s="5"/>
+      <c r="Q63" s="5"/>
     </row>
     <row r="64" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B64" s="3">
@@ -3491,35 +3494,35 @@
       <c r="F64" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G64" s="3">
+      <c r="G64" s="5">
         <v>17.5</v>
       </c>
-      <c r="H64" s="3">
+      <c r="H64" s="5">
         <v>11.53</v>
       </c>
-      <c r="I64" s="3">
+      <c r="I64" s="5">
         <v>14.93</v>
       </c>
-      <c r="J64" s="3">
+      <c r="J64" s="5">
         <v>17.39</v>
       </c>
-      <c r="K64" s="3">
+      <c r="K64" s="5">
         <v>17.309999999999999</v>
       </c>
-      <c r="L64" s="3">
+      <c r="L64" s="5">
         <v>12.78</v>
       </c>
-      <c r="M64" s="3">
+      <c r="M64" s="5">
         <v>6.54</v>
       </c>
-      <c r="N64" s="3">
+      <c r="N64" s="5">
         <v>1.86</v>
       </c>
-      <c r="O64" s="3">
+      <c r="O64" s="5">
         <v>0.16</v>
       </c>
-      <c r="P64" s="3"/>
-      <c r="Q64" s="3"/>
+      <c r="P64" s="5"/>
+      <c r="Q64" s="5"/>
     </row>
     <row r="65" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B65" s="3">
@@ -3537,35 +3540,35 @@
       <c r="F65" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G65" s="3">
+      <c r="G65" s="5">
         <v>18.23</v>
       </c>
-      <c r="H65" s="3">
+      <c r="H65" s="5">
         <v>11.89</v>
       </c>
-      <c r="I65" s="3">
+      <c r="I65" s="5">
         <v>15.04</v>
       </c>
-      <c r="J65" s="3">
+      <c r="J65" s="5">
         <v>17.72</v>
       </c>
-      <c r="K65" s="3">
+      <c r="K65" s="5">
         <v>16.79</v>
       </c>
-      <c r="L65" s="3">
+      <c r="L65" s="5">
         <v>12.48</v>
       </c>
-      <c r="M65" s="3">
+      <c r="M65" s="5">
         <v>5.9</v>
       </c>
-      <c r="N65" s="3">
+      <c r="N65" s="5">
         <v>1.81</v>
       </c>
-      <c r="O65" s="3">
+      <c r="O65" s="5">
         <v>0.14000000000000001</v>
       </c>
-      <c r="P65" s="3"/>
-      <c r="Q65" s="3"/>
+      <c r="P65" s="5"/>
+      <c r="Q65" s="5"/>
     </row>
     <row r="66" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B66" s="3">
@@ -3583,37 +3586,37 @@
       <c r="F66" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G66" s="3">
+      <c r="G66" s="5">
         <v>16.13</v>
       </c>
-      <c r="H66" s="3">
+      <c r="H66" s="5">
         <v>17.309999999999999</v>
       </c>
-      <c r="I66" s="3">
+      <c r="I66" s="5">
         <v>18.940000000000001</v>
       </c>
-      <c r="J66" s="3">
+      <c r="J66" s="5">
         <v>17.25</v>
       </c>
-      <c r="K66" s="3">
+      <c r="K66" s="5">
         <v>12.52</v>
       </c>
-      <c r="L66" s="3">
+      <c r="L66" s="5">
         <v>8.16</v>
       </c>
-      <c r="M66" s="3">
+      <c r="M66" s="5">
         <v>4.91</v>
       </c>
-      <c r="N66" s="3">
+      <c r="N66" s="5">
         <v>2.75</v>
       </c>
-      <c r="O66" s="3">
+      <c r="O66" s="5">
         <v>1.52</v>
       </c>
-      <c r="P66" s="3">
+      <c r="P66" s="5">
         <v>0.48</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="Q66" s="5">
         <v>0.03</v>
       </c>
     </row>
@@ -3633,37 +3636,37 @@
       <c r="F67" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G67" s="3">
+      <c r="G67" s="5">
         <v>18.09</v>
       </c>
-      <c r="H67" s="3">
+      <c r="H67" s="5">
         <v>17.3</v>
       </c>
-      <c r="I67" s="3">
+      <c r="I67" s="5">
         <v>19.059999999999999</v>
       </c>
-      <c r="J67" s="3">
+      <c r="J67" s="5">
         <v>17.07</v>
       </c>
-      <c r="K67" s="3">
+      <c r="K67" s="5">
         <v>12.24</v>
       </c>
-      <c r="L67" s="3">
+      <c r="L67" s="5">
         <v>7.62</v>
       </c>
-      <c r="M67" s="3">
+      <c r="M67" s="5">
         <v>4.54</v>
       </c>
-      <c r="N67" s="3">
+      <c r="N67" s="5">
         <v>2.35</v>
       </c>
-      <c r="O67" s="3">
+      <c r="O67" s="5">
         <v>1.18</v>
       </c>
-      <c r="P67" s="3">
+      <c r="P67" s="5">
         <v>0.53</v>
       </c>
-      <c r="Q67" s="3">
+      <c r="Q67" s="5">
         <v>0.01</v>
       </c>
     </row>
@@ -3683,35 +3686,35 @@
       <c r="F68" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G68" s="3">
+      <c r="G68" s="5">
         <v>17.54</v>
       </c>
-      <c r="H68" s="3">
+      <c r="H68" s="5">
         <v>11.12</v>
       </c>
-      <c r="I68" s="3">
+      <c r="I68" s="5">
         <v>14.37</v>
       </c>
-      <c r="J68" s="3">
+      <c r="J68" s="5">
         <v>17.23</v>
       </c>
-      <c r="K68" s="3">
+      <c r="K68" s="5">
         <v>17.579999999999998</v>
       </c>
-      <c r="L68" s="3">
+      <c r="L68" s="5">
         <v>12.95</v>
       </c>
-      <c r="M68" s="3">
+      <c r="M68" s="5">
         <v>6.78</v>
       </c>
-      <c r="N68" s="3">
+      <c r="N68" s="5">
         <v>2.11</v>
       </c>
-      <c r="O68" s="3">
+      <c r="O68" s="5">
         <v>0.32</v>
       </c>
-      <c r="P68" s="3"/>
-      <c r="Q68" s="3"/>
+      <c r="P68" s="5"/>
+      <c r="Q68" s="5"/>
     </row>
     <row r="69" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B69" s="3">
@@ -3729,35 +3732,35 @@
       <c r="F69" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G69" s="3">
+      <c r="G69" s="5">
         <v>17.170000000000002</v>
       </c>
-      <c r="H69" s="3">
+      <c r="H69" s="5">
         <v>11.13</v>
       </c>
-      <c r="I69" s="3">
+      <c r="I69" s="5">
         <v>14.47</v>
       </c>
-      <c r="J69" s="3">
+      <c r="J69" s="5">
         <v>17.37</v>
       </c>
-      <c r="K69" s="3">
+      <c r="K69" s="5">
         <v>17.46</v>
       </c>
-      <c r="L69" s="3">
+      <c r="L69" s="5">
         <v>13.09</v>
       </c>
-      <c r="M69" s="3">
+      <c r="M69" s="5">
         <v>6.88</v>
       </c>
-      <c r="N69" s="3">
+      <c r="N69" s="5">
         <v>2.12</v>
       </c>
-      <c r="O69" s="3">
+      <c r="O69" s="5">
         <v>0.32</v>
       </c>
-      <c r="P69" s="3"/>
-      <c r="Q69" s="3"/>
+      <c r="P69" s="5"/>
+      <c r="Q69" s="5"/>
     </row>
     <row r="70" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B70" s="3">
@@ -3775,37 +3778,37 @@
       <c r="F70" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G70" s="3">
+      <c r="G70" s="5">
         <v>15.57</v>
       </c>
-      <c r="H70" s="3">
+      <c r="H70" s="5">
         <v>17.45</v>
       </c>
-      <c r="I70" s="3">
+      <c r="I70" s="5">
         <v>19.52</v>
       </c>
-      <c r="J70" s="3">
+      <c r="J70" s="5">
         <v>16.309999999999999</v>
       </c>
-      <c r="K70" s="3">
+      <c r="K70" s="5">
         <v>10.3</v>
       </c>
-      <c r="L70" s="3">
+      <c r="L70" s="5">
         <v>7.21</v>
       </c>
-      <c r="M70" s="3">
+      <c r="M70" s="5">
         <v>6.33</v>
       </c>
-      <c r="N70" s="3">
+      <c r="N70" s="5">
         <v>4.41</v>
       </c>
-      <c r="O70" s="3">
+      <c r="O70" s="5">
         <v>2.17</v>
       </c>
-      <c r="P70" s="3">
+      <c r="P70" s="5">
         <v>0.71</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="Q70" s="5">
         <v>0.02</v>
       </c>
     </row>
@@ -3825,37 +3828,37 @@
       <c r="F71" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G71" s="3">
+      <c r="G71" s="5">
         <v>16.3</v>
       </c>
-      <c r="H71" s="3">
+      <c r="H71" s="5">
         <v>17.89</v>
       </c>
-      <c r="I71" s="3">
+      <c r="I71" s="5">
         <v>19.71</v>
       </c>
-      <c r="J71" s="3">
+      <c r="J71" s="5">
         <v>15.92</v>
       </c>
-      <c r="K71" s="3">
+      <c r="K71" s="5">
         <v>10.29</v>
       </c>
-      <c r="L71" s="3">
+      <c r="L71" s="5">
         <v>7.51</v>
       </c>
-      <c r="M71" s="3">
+      <c r="M71" s="5">
         <v>5.78</v>
       </c>
-      <c r="N71" s="3">
+      <c r="N71" s="5">
         <v>3.92</v>
       </c>
-      <c r="O71" s="3">
+      <c r="O71" s="5">
         <v>1.98</v>
       </c>
-      <c r="P71" s="3">
+      <c r="P71" s="5">
         <v>0.69</v>
       </c>
-      <c r="Q71" s="3">
+      <c r="Q71" s="5">
         <v>0.01</v>
       </c>
     </row>
@@ -3875,35 +3878,35 @@
       <c r="F72" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G72" s="3">
+      <c r="G72" s="5">
         <v>16.350000000000001</v>
       </c>
-      <c r="H72" s="3">
+      <c r="H72" s="5">
         <v>11.82</v>
       </c>
-      <c r="I72" s="3">
+      <c r="I72" s="5">
         <v>15.2</v>
       </c>
-      <c r="J72" s="3">
+      <c r="J72" s="5">
         <v>17.579999999999998</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="5">
         <v>17.2</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="5">
         <v>13.16</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="5">
         <v>6.96</v>
       </c>
-      <c r="N72" s="3">
+      <c r="N72" s="5">
         <v>1.68</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="5">
         <v>0.05</v>
       </c>
-      <c r="P72" s="3"/>
-      <c r="Q72" s="3"/>
+      <c r="P72" s="5"/>
+      <c r="Q72" s="5"/>
     </row>
     <row r="73" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B73" s="3">
@@ -3921,35 +3924,35 @@
       <c r="F73" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G73" s="3">
+      <c r="G73" s="5">
         <v>18.420000000000002</v>
       </c>
-      <c r="H73" s="3">
+      <c r="H73" s="5">
         <v>12.59</v>
       </c>
-      <c r="I73" s="3">
+      <c r="I73" s="5">
         <v>15.77</v>
       </c>
-      <c r="J73" s="3">
+      <c r="J73" s="5">
         <v>17.329999999999998</v>
       </c>
-      <c r="K73" s="3">
+      <c r="K73" s="5">
         <v>16.36</v>
       </c>
-      <c r="L73" s="3">
+      <c r="L73" s="5">
         <v>12.15</v>
       </c>
-      <c r="M73" s="3">
+      <c r="M73" s="5">
         <v>5.9</v>
       </c>
-      <c r="N73" s="3">
+      <c r="N73" s="5">
         <v>1.42</v>
       </c>
-      <c r="O73" s="3">
+      <c r="O73" s="5">
         <v>0.05</v>
       </c>
-      <c r="P73" s="3"/>
-      <c r="Q73" s="3"/>
+      <c r="P73" s="5"/>
+      <c r="Q73" s="5"/>
     </row>
     <row r="74" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B74" s="3">
@@ -3967,37 +3970,37 @@
       <c r="F74" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G74" s="3">
+      <c r="G74" s="5">
         <v>18.68</v>
       </c>
-      <c r="H74" s="3">
+      <c r="H74" s="5">
         <v>13.84</v>
       </c>
-      <c r="I74" s="3">
+      <c r="I74" s="5">
         <v>17.239999999999998</v>
       </c>
-      <c r="J74" s="3">
+      <c r="J74" s="5">
         <v>18.07</v>
       </c>
-      <c r="K74" s="3">
+      <c r="K74" s="5">
         <v>13.72</v>
       </c>
-      <c r="L74" s="3">
+      <c r="L74" s="5">
         <v>9.5500000000000007</v>
       </c>
-      <c r="M74" s="3">
+      <c r="M74" s="5">
         <v>4.7699999999999996</v>
       </c>
-      <c r="N74" s="3">
+      <c r="N74" s="5">
         <v>2.44</v>
       </c>
-      <c r="O74" s="3">
+      <c r="O74" s="5">
         <v>1.21</v>
       </c>
-      <c r="P74" s="3">
+      <c r="P74" s="5">
         <v>0.48</v>
       </c>
-      <c r="Q74" s="3">
+      <c r="Q74" s="5">
         <v>0</v>
       </c>
     </row>
@@ -4017,37 +4020,37 @@
       <c r="F75" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G75" s="3">
+      <c r="G75" s="5">
         <v>21.11</v>
       </c>
-      <c r="H75" s="3">
+      <c r="H75" s="5">
         <v>14.14</v>
       </c>
-      <c r="I75" s="3">
+      <c r="I75" s="5">
         <v>17.14</v>
       </c>
-      <c r="J75" s="3">
+      <c r="J75" s="5">
         <v>17.43</v>
       </c>
-      <c r="K75" s="3">
+      <c r="K75" s="5">
         <v>13.18</v>
       </c>
-      <c r="L75" s="3">
+      <c r="L75" s="5">
         <v>8.64</v>
       </c>
-      <c r="M75" s="3">
+      <c r="M75" s="5">
         <v>4.75</v>
       </c>
-      <c r="N75" s="3">
+      <c r="N75" s="5">
         <v>2.31</v>
       </c>
-      <c r="O75" s="3">
+      <c r="O75" s="5">
         <v>0.97</v>
       </c>
-      <c r="P75" s="3">
+      <c r="P75" s="5">
         <v>0.33</v>
       </c>
-      <c r="Q75" s="3">
+      <c r="Q75" s="5">
         <v>0</v>
       </c>
     </row>

--- a/Pasta_3.xlsx
+++ b/Pasta_3.xlsx
@@ -89,9 +89,6 @@
     <t>INEP</t>
   </si>
   <si>
-    <t>3º ANO EM</t>
-  </si>
-  <si>
     <t>BRASIL</t>
   </si>
   <si>
@@ -108,6 +105,9 @@
   </si>
   <si>
     <t>EEMTI PROFESSORA MARIA MARGARIDA DE CASTRO ALMEIDA</t>
+  </si>
+  <si>
+    <t>3º ANO</t>
   </si>
 </sst>
 </file>
@@ -525,13 +525,13 @@
         <v>23078340</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" s="3">
         <v>2017</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>16</v>
@@ -571,13 +571,13 @@
         <v>23078340</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D3" s="3">
         <v>2017</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>17</v>
@@ -619,13 +619,13 @@
         <v>23078340</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4" s="3">
         <v>2019</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>16</v>
@@ -665,13 +665,13 @@
         <v>23078340</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D5" s="3">
         <v>2019</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>17</v>
@@ -713,13 +713,13 @@
         <v>23078340</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D6" s="3">
         <v>2023</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>16</v>
@@ -759,13 +759,13 @@
         <v>23078340</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D7" s="3">
         <v>2023</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>17</v>
@@ -807,13 +807,13 @@
         <v>23078340</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D8" s="3">
         <v>2025</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>16</v>
@@ -853,13 +853,13 @@
         <v>23078340</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" s="3">
         <v>2025</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>17</v>
@@ -909,7 +909,7 @@
         <v>2017</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>16</v>
@@ -955,7 +955,7 @@
         <v>2017</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>17</v>
@@ -1003,7 +1003,7 @@
         <v>2019</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>16</v>
@@ -1049,7 +1049,7 @@
         <v>2019</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>17</v>
@@ -1099,7 +1099,7 @@
         <v>2021</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>16</v>
@@ -1145,7 +1145,7 @@
         <v>2021</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>17</v>
@@ -1195,7 +1195,7 @@
         <v>2023</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>16</v>
@@ -1241,7 +1241,7 @@
         <v>2023</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>17</v>
@@ -1291,7 +1291,7 @@
         <v>2025</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>16</v>
@@ -1337,7 +1337,7 @@
         <v>2025</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>17</v>
@@ -1387,7 +1387,7 @@
         <v>2017</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>16</v>
@@ -1433,7 +1433,7 @@
         <v>2017</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>17</v>
@@ -1481,7 +1481,7 @@
         <v>2019</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>16</v>
@@ -1527,7 +1527,7 @@
         <v>2019</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>17</v>
@@ -1577,7 +1577,7 @@
         <v>2021</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>16</v>
@@ -1623,7 +1623,7 @@
         <v>2021</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>17</v>
@@ -1673,7 +1673,7 @@
         <v>2023</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>16</v>
@@ -1719,7 +1719,7 @@
         <v>2023</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>17</v>
@@ -1769,7 +1769,7 @@
         <v>2025</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>16</v>
@@ -1815,7 +1815,7 @@
         <v>2025</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>17</v>
@@ -1859,13 +1859,13 @@
         <v>23071370</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D30" s="3">
         <v>2017</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>16</v>
@@ -1905,13 +1905,13 @@
         <v>23071370</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D31" s="3">
         <v>2017</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>17</v>
@@ -1953,13 +1953,13 @@
         <v>23071370</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D32" s="3">
         <v>2019</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>16</v>
@@ -1999,13 +1999,13 @@
         <v>23071370</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D33" s="3">
         <v>2019</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>17</v>
@@ -2049,13 +2049,13 @@
         <v>23071370</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D34" s="3">
         <v>2021</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>16</v>
@@ -2095,13 +2095,13 @@
         <v>23071370</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D35" s="3">
         <v>2021</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>17</v>
@@ -2145,13 +2145,13 @@
         <v>23071370</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D36" s="3">
         <v>2023</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>16</v>
@@ -2191,13 +2191,13 @@
         <v>23071370</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D37" s="3">
         <v>2023</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>17</v>
@@ -2241,13 +2241,13 @@
         <v>23071370</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D38" s="3">
         <v>2025</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>16</v>
@@ -2287,13 +2287,13 @@
         <v>23071370</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D39" s="3">
         <v>2025</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>17</v>
@@ -2337,13 +2337,13 @@
         <v>23186364</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D40" s="3">
         <v>2017</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>16</v>
@@ -2383,13 +2383,13 @@
         <v>23186364</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D41" s="3">
         <v>2017</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>17</v>
@@ -2431,13 +2431,13 @@
         <v>23186364</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D42" s="3">
         <v>2019</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>16</v>
@@ -2477,13 +2477,13 @@
         <v>23186364</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D43" s="3">
         <v>2019</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>17</v>
@@ -2527,13 +2527,13 @@
         <v>23186364</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D44" s="3">
         <v>2021</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>16</v>
@@ -2573,13 +2573,13 @@
         <v>23186364</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D45" s="3">
         <v>2021</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>17</v>
@@ -2623,13 +2623,13 @@
         <v>23186364</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D46" s="3">
         <v>2023</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>16</v>
@@ -2669,13 +2669,13 @@
         <v>23186364</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D47" s="3">
         <v>2023</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>17</v>
@@ -2719,13 +2719,13 @@
         <v>23186364</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D48" s="3">
         <v>2025</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>16</v>
@@ -2765,13 +2765,13 @@
         <v>23186364</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D49" s="3">
         <v>2025</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>17</v>
@@ -2815,13 +2815,13 @@
         <v>23073713</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D50" s="3">
         <v>2017</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>16</v>
@@ -2861,13 +2861,13 @@
         <v>23073713</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D51" s="3">
         <v>2017</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>17</v>
@@ -2909,13 +2909,13 @@
         <v>23073713</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D52" s="3">
         <v>2019</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>16</v>
@@ -2955,13 +2955,13 @@
         <v>23073713</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D53" s="3">
         <v>2019</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>17</v>
@@ -3003,13 +3003,13 @@
         <v>23073713</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D54" s="3">
         <v>2021</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>16</v>
@@ -3049,13 +3049,13 @@
         <v>23073713</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D55" s="3">
         <v>2021</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>17</v>
@@ -3099,13 +3099,13 @@
         <v>23073713</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D56" s="3">
         <v>2023</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>16</v>
@@ -3145,13 +3145,13 @@
         <v>23073713</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D57" s="3">
         <v>2023</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>17</v>
@@ -3195,13 +3195,13 @@
         <v>23073713</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D58" s="3">
         <v>2025</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>16</v>
@@ -3241,13 +3241,13 @@
         <v>23073713</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D59" s="3">
         <v>2025</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>17</v>
@@ -3291,13 +3291,13 @@
         <v>23</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D60" s="3">
         <v>2019</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>17</v>
@@ -3341,13 +3341,13 @@
         <v>11</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D61" s="3">
         <v>2019</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>17</v>
@@ -3391,13 +3391,13 @@
         <v>23</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D62" s="3">
         <v>2019</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>16</v>
@@ -3437,13 +3437,13 @@
         <v>11</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D63" s="3">
         <v>2019</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>16</v>
@@ -3483,13 +3483,13 @@
         <v>23</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D64" s="3">
         <v>2023</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>16</v>
@@ -3529,13 +3529,13 @@
         <v>11</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D65" s="3">
         <v>2023</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F65" s="4" t="s">
         <v>16</v>
@@ -3575,13 +3575,13 @@
         <v>23</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D66" s="3">
         <v>2023</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>17</v>
@@ -3625,13 +3625,13 @@
         <v>11</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D67" s="3">
         <v>2023</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>17</v>
@@ -3675,13 +3675,13 @@
         <v>23</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D68" s="3">
         <v>2025</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>16</v>
@@ -3721,13 +3721,13 @@
         <v>11</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D69" s="3">
         <v>2025</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>16</v>
@@ -3767,13 +3767,13 @@
         <v>23</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D70" s="3">
         <v>2025</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>17</v>
@@ -3817,13 +3817,13 @@
         <v>11</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D71" s="3">
         <v>2025</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>17</v>
@@ -3867,13 +3867,13 @@
         <v>23</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D72" s="3">
         <v>2021</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>16</v>
@@ -3913,13 +3913,13 @@
         <v>11</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D73" s="3">
         <v>2021</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>16</v>
@@ -3959,13 +3959,13 @@
         <v>23</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D74" s="3">
         <v>2021</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>17</v>
@@ -4009,13 +4009,13 @@
         <v>11</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D75" s="3">
         <v>2021</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>17</v>
